--- a/laporan_padel_dki_jakarta_2026-10-13.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-13.xlsx
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp3.280.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.732.991</t>
+          <t>Rp4.430.989</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.081.500</t>
+          <t>Rp8.569.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp13.659.000</t>
+          <t>Rp12.663.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.218.000</t>
+          <t>Rp3.618.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp6.060.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp6.075.000</t>
+          <t>Rp6.775.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.760.000</t>
+          <t>Rp6.048.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp549.000</t>
+          <t>Rp749.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.275.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp7.900.000</t>
+          <t>Rp10.560.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp420.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.984.000</t>
+          <t>Rp4.682.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.035.000</t>
+          <t>Rp695.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp2.215.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.475.000</t>
+          <t>Rp3.725.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.972.000</t>
+          <t>Rp3.773.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>28</v>
       </c>
       <c r="D99" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.850.000</t>
+          <t>Rp8.200.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.580.000</t>
+          <t>Rp6.980.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.025.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.246.000</t>
+          <t>Rp1.595.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>17</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp499.000</t>
+          <t>Rp899.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp9.840.000</t>
+          <t>Rp11.232.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp825.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.820.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp9.450.000</t>
+          <t>Rp9.950.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp8.703.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.950.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp11.550.000</t>
+          <t>Rp12.650.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp9.650.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.500.000</t>
+          <t>Rp9.200.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.320.000</t>
+          <t>Rp4.545.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.055.000</t>
+          <t>Rp2.235.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.525.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp8.050.000</t>
+          <t>Rp9.390.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.085.000</t>
+          <t>Rp11.365.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp69.000</t>
+          <t>Rp207.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.779.000</t>
+          <t>Rp7.835.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.180.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.184.000</t>
+          <t>Rp3.742.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.828.000</t>
+          <t>Rp2.997.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp594.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.175.000</t>
+          <t>Rp3.725.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.160.000</t>
+          <t>Rp3.660.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp10.560.000</t>
+          <t>Rp10.805.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>67</v>
       </c>
       <c r="D35" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.576.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp5.925.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp19.150.000</t>
+          <t>Rp19.750.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>144</v>
       </c>
       <c r="D51" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.210.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.415.000</t>
+          <t>Rp5.585.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.239.000</t>
+          <t>Rp1.539.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp850.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp310.000</t>
+          <t>Rp1.430.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.841.000</t>
+          <t>Rp4.230.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp16.060.000</t>
+          <t>Rp16.760.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.630.000</t>
+          <t>Rp4.020.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.824.994</t>
+          <t>Rp3.949.994</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.860.000</t>
+          <t>Rp3.285.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.670.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.795.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.570.000</t>
+          <t>Rp1.720.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>72</v>
       </c>
       <c r="D42" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-13.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-13.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.740.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.391.000</t>
+          <t>Rp2.589.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.430.989</t>
+          <t>Rp4.680.989</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.569.000</t>
+          <t>Rp8.697.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.618.000</t>
+          <t>Rp3.416.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.529.000</t>
+          <t>Rp2.628.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.082.000</t>
+          <t>Rp3.180.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.870.000</t>
+          <t>Rp2.010.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.970.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.345.000</t>
+          <t>Rp3.143.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>54</v>
       </c>
       <c r="D57" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.660.000</t>
+          <t>Rp1.790.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp1.881.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.682.000</t>
+          <t>Rp3.486.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.773.000</t>
+          <t>Rp3.772.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.598.000</t>
+          <t>Rp1.697.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.395.000</t>
+          <t>Rp3.930.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.997.000</t>
+          <t>Rp2.097.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp2.610.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.025.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp13.850.000</t>
+          <t>Rp14.000.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.320.000</t>
+          <t>Rp3.520.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp33.950.000</t>
+          <t>Rp33.450.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.525.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.475.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp1.740.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.225.000</t>
+          <t>Rp5.775.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7145,21 +7145,21 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.598.000</t>
+          <t>Rp4.760.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp81.000 - Rp175.000</t>
+          <t>Rp10.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7176,16 +7176,16 @@
         <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp419.000</t>
+          <t>Rp719.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp8.400.000</t>
+          <t>Rp9.800.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>174</v>
       </c>
       <c r="D45" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp22.400.000</t>
+          <t>Rp23.400.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>102</v>
       </c>
       <c r="D46" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp410.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>90</v>
       </c>
       <c r="D52" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.585.000</t>
+          <t>Rp6.945.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.290.000</t>
+          <t>Rp7.980.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp16.760.000</t>
+          <t>Rp17.460.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.285.000</t>
+          <t>Rp3.645.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.257.000</t>
+          <t>Rp1.382.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-13.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-13.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.589.000</t>
+          <t>Rp2.739.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.680.989</t>
+          <t>Rp5.029.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.697.000</t>
+          <t>Rp11.172.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.914.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp626.000</t>
+          <t>Rp814.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.416.000</t>
+          <t>Rp4.014.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.180.000</t>
+          <t>Rp3.476.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.270.000</t>
+          <t>Rp4.090.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp570.000</t>
+          <t>Rp1.410.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.762.000</t>
+          <t>Rp9.711.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp2.730.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp6.775.000</t>
+          <t>Rp8.325.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.143.000</t>
+          <t>Rp3.941.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.048.000</t>
+          <t>Rp6.912.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>54</v>
       </c>
       <c r="D57" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.790.000</t>
+          <t>Rp1.630.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp798.000</t>
+          <t>Rp1.196.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp10.560.000</t>
+          <t>Rp10.060.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.985.000</t>
+          <t>Rp3.185.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp1.020.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>32</v>
       </c>
       <c r="D67" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp520.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.486.000</t>
+          <t>Rp4.582.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp6.887.500</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp5.680.000</t>
+          <t>Rp5.925.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.725.000</t>
+          <t>Rp4.225.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.772.000</t>
+          <t>Rp4.868.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp7.225.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp2.280.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.695.000</t>
+          <t>Rp4.055.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp620.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.200.000</t>
+          <t>Rp9.950.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.635.000</t>
+          <t>Rp6.215.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.097.000</t>
+          <t>Rp2.497.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.725.000</t>
+          <t>Rp5.025.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.595.000</t>
+          <t>Rp1.944.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.180.000</t>
+          <t>Rp1.530.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp770.000</t>
+          <t>Rp1.155.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp30.470.000</t>
+          <t>Rp29.810.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp899.000</t>
+          <t>Rp1.699.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp788.000</t>
+          <t>Rp1.186.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp14.000.000</t>
+          <t>Rp14.400.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp5.370.000</t>
+          <t>Rp5.920.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp8.950.000</t>
+          <t>Rp8.150.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp8.703.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp8.584.000</t>
+          <t>Rp8.804.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp9.950.000</t>
+          <t>Rp12.950.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.540.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp12.650.000</t>
+          <t>Rp16.250.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp9.650.000</t>
+          <t>Rp9.400.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.905.000</t>
+          <t>Rp15.565.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.200.000</t>
+          <t>Rp9.550.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp1.910.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp4.425.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.235.000</t>
+          <t>Rp3.210.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.075.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.945.000</t>
+          <t>Rp4.230.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.575.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.390.000</t>
+          <t>Rp10.410.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp207.000</t>
+          <t>Rp414.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp9.065.000</t>
+          <t>Rp11.125.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.750.000</t>
+          <t>Rp8.450.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.835.000</t>
+          <t>Rp8.543.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.180.000</t>
+          <t>Rp2.780.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.742.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.740.000</t>
+          <t>Rp3.040.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.775.000</t>
+          <t>Rp5.375.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7049,24 +7049,24 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp891.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp75.000 - Rp99.000</t>
         </is>
       </c>
     </row>
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.700.000</t>
+          <t>Rp21.000.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.760.000</t>
+          <t>Rp4.666.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.870.000</t>
+          <t>Rp5.370.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.725.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.660.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp10.805.000</t>
+          <t>Rp11.050.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp9.800.000</t>
+          <t>Rp11.925.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.925.000</t>
+          <t>Rp6.475.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.916.000</t>
+          <t>Rp2.204.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp350.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp19.750.000</t>
+          <t>Rp20.250.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>120</v>
       </c>
       <c r="D41" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp599.000</t>
+          <t>Rp2.599.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>102</v>
       </c>
       <c r="D46" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp410.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>108</v>
       </c>
       <c r="D48" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>98</v>
       </c>
       <c r="D50" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp4.120.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.210.000</t>
+          <t>Rp1.580.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp825.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.970.000</t>
+          <t>Rp6.225.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.465.000</t>
+          <t>Rp4.755.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.430.000</t>
+          <t>Rp1.590.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.230.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.460.000</t>
+          <t>Rp16.980.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp135.000</t>
+          <t>Rp775.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.020.000</t>
+          <t>Rp3.240.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.034.000</t>
+          <t>Rp1.238.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.949.994</t>
+          <t>Rp4.199.994</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.645.000</t>
+          <t>Rp4.215.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp290.000</t>
+          <t>Rp435.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp3.705.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.795.000</t>
+          <t>Rp615.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>51</v>
       </c>
       <c r="D38" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.110.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.933.000</t>
+          <t>Rp2.230.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp6.485.000</t>
+          <t>Rp5.985.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.382.000</t>
+          <t>Rp2.058.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-13.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-13.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.740.000</t>
+          <t>Rp1.580.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.029.988</t>
+          <t>Rp5.177.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.172.000</t>
+          <t>Rp11.722.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.475.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.090.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.010.000</t>
+          <t>Rp2.205.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.912.000</t>
+          <t>Rp7.488.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>32</v>
       </c>
       <c r="D67" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp520.000</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp695.000</t>
+          <t>Rp940.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp5.075.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp5.925.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.868.000</t>
+          <t>Rp5.664.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>36</v>
       </c>
       <c r="D86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.497.000</t>
+          <t>Rp2.697.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.610.000</t>
+          <t>Rp3.420.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp29.810.000</t>
+          <t>Rp30.310.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.186.000</t>
+          <t>Rp1.584.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp6.199.000</t>
+          <t>Rp5.599.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp372.000</t>
+          <t>Rp549.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp8.703.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp8.804.000</t>
+          <t>Rp9.324.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp16.250.000</t>
+          <t>Rp16.800.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.565.000</t>
+          <t>Rp18.095.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.550.000</t>
+          <t>Rp10.150.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.210.000</t>
+          <t>Rp3.329.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.410.000</t>
+          <t>Rp10.210.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp8.450.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.543.000</t>
+          <t>Rp8.642.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp3.742.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.346.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.666.000</t>
+          <t>Rp4.851.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.050.000</t>
+          <t>Rp11.295.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp11.925.000</t>
+          <t>Rp12.075.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>67</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.576.000</t>
+          <t>Rp6.328.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.204.000</t>
+          <t>Rp2.780.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp20.250.000</t>
+          <t>Rp20.950.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>174</v>
       </c>
       <c r="D45" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp23.400.000</t>
+          <t>Rp23.900.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>108</v>
       </c>
       <c r="D48" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>96</v>
       </c>
       <c r="D49" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp7.416.000</t>
+          <t>Rp8.812.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>98</v>
       </c>
       <c r="D50" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.120.000</t>
+          <t>Rp4.460.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.945.000</t>
+          <t>Rp7.075.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.190.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp630.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.238.000</t>
+          <t>Rp1.437.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp5.985.000</t>
+          <t>Rp6.235.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.058.000</t>
+          <t>Rp2.396.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-13.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-13.xlsx
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.722.000</t>
+          <t>Rp11.997.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp1.090.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp4.225.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.058.500</t>
+          <t>Rp14.241.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.950.000</t>
+          <t>Rp10.450.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp590.000</t>
+          <t>Rp1.180.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.215.000</t>
+          <t>Rp4.635.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp14.400.000</t>
+          <t>Rp14.550.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp10.150.000</t>
+          <t>Rp10.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.545.000</t>
+          <t>Rp5.045.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp414.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.125.000</t>
+          <t>Rp11.400.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.040.000</t>
+          <t>Rp3.240.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.851.000</t>
+          <t>Rp4.871.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp5.370.000</t>
+          <t>Rp5.710.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp12.075.000</t>
+          <t>Rp12.350.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp20.950.000</t>
+          <t>Rp21.175.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>120</v>
       </c>
       <c r="D41" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.599.000</t>
+          <t>Rp2.999.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>98</v>
       </c>
       <c r="D50" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.460.000</t>
+          <t>Rp4.610.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.225.000</t>
+          <t>Rp6.375.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>120</v>
       </c>
       <c r="D37" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.059.000</t>
+          <t>Rp3.158.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
